--- a/Inventario el Gremio 1ro de Agosto.xlsx
+++ b/Inventario el Gremio 1ro de Agosto.xlsx
@@ -10,28 +10,6 @@
   <definedNames/>
   <calcPr/>
 </workbook>
-</file>
-
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
-  <authors>
-    <author>tc={9b59e7a5-8741-4cda-b1d4-3cd57a11fad4}</author>
-  </authors>
-  <commentList>
-    <comment authorId="0" xr:uid="{9b59e7a5-8741-4cda-b1d4-3cd57a11fad4}" ref="H2">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	Las Cat son
-Accesorios
-Juegos de Mesa
-TCG
-</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
